--- a/Retro/Retro-BOM.xlsx
+++ b/Retro/Retro-BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\NAS\Data\Workfiles\BMD\Projects\Atari\Breakout\github\Retro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579A367E-39A4-4D30-B9FD-B1EAD2C70281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172358E0-68E1-4805-94E4-4D6154C0F6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88885ED0-DCBD-4D32-912E-6D1BE46CB9BC}"/>
+    <workbookView xWindow="4185" yWindow="525" windowWidth="23310" windowHeight="14640" activeTab="1" xr2:uid="{88885ED0-DCBD-4D32-912E-6D1BE46CB9BC}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="313">
   <si>
     <t>Value</t>
   </si>
@@ -906,12 +906,6 @@
     <t>5533A</t>
   </si>
   <si>
-    <t>Motorola</t>
-  </si>
-  <si>
-    <t>4526</t>
-  </si>
-  <si>
     <t>T.I.</t>
   </si>
   <si>
@@ -928,6 +922,60 @@
   </si>
   <si>
     <t>PSU5a 5V 3A Regulator in TO-220 form Factor</t>
+  </si>
+  <si>
+    <t>Tested</t>
+  </si>
+  <si>
+    <t>Works</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>@Ramex2099</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Fairchild</t>
+  </si>
+  <si>
+    <t>Some parts work paritally. They disable DOUT when writing so the bricks disappear between start game and 1st serve (WE held constantly low). They also don't properly set the 2nd wall of bricks.</t>
+  </si>
+  <si>
+    <t>Partially</t>
+  </si>
+  <si>
+    <t>ByteMind</t>
+  </si>
+  <si>
+    <t>93410/11</t>
+  </si>
+  <si>
+    <t>93420/21</t>
+  </si>
+  <si>
+    <t>BlockDQ?</t>
+  </si>
+  <si>
+    <t>Works-Partially</t>
+  </si>
+  <si>
+    <t>Datasheets show that DOUT is block (High-Z or High) when WE is low.</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>At this point I recommend use the Signetics N82S16, N82LS16 or N82S17 Part - Paul</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1046,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1033,16 +1081,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2723,7 +2783,7 @@
         <v>268</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="3" t="s">
@@ -2750,7 +2810,7 @@
         <v>191</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>192</v>
@@ -2779,7 +2839,7 @@
         <v>20</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>187</v>
@@ -2805,7 +2865,7 @@
         <v>189</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>190</v>
@@ -2834,7 +2894,7 @@
         <v>19</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>188</v>
@@ -3246,7 +3306,7 @@
         <v>25</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="3" t="s">
@@ -3485,17 +3545,6 @@
       <c r="I88" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="89" spans="1:9">
-      <c r="A89" s="12"/>
-      <c r="B89" s="12"/>
-      <c r="C89" s="12"/>
-      <c r="D89" s="12"/>
-      <c r="E89" s="12"/>
-      <c r="F89" s="12"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="12"/>
-      <c r="I89" s="12"/>
     </row>
     <row r="91" spans="1:9" ht="18">
       <c r="A91" s="9" t="s">
@@ -3637,118 +3686,212 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D56C89DF-E81B-4E7B-B184-4275B68F90B2}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="8.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.875" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9" style="18"/>
+    <col min="8" max="8" width="12.625" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="14" customFormat="1" ht="15">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:9" s="12" customFormat="1" ht="15">
+      <c r="A1" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>269</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="13" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>276</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="13">
         <v>2700</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="13">
         <v>2701</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>278</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>267</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="17" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>283</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="13" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>286</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="13" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>289</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="B8" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>291</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>281</v>
+        <v>301</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15">
+      <c r="A12" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="48.75" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="20"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:H13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>